--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0144.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0144.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Chiếc thuyền Gondola chất đầy hàng hóa như đang nói: "Đưa tiền đây, ta cho đồ ngon!"</t>
+          <t>Chiếc thuyền Gondola chất đầy hàng hóa như đang nói: "Đưa tiền đây, tao cho đồ ngon!"</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Hắn bị yểm bùa gì đó à? Ta đã đọc về những triệu chứng kiểu này trong kho lưu trữ của Hội trước đây.</t>
+          <t>Hắn bị yểm bùa gì đó à? Tao đã đọc về những triệu chứng kiểu này trong kho lưu trữ của Hội trước đây.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hử? Ta chỉ làm theo những gì ghi trong kho lưu trữ thôi mà...</t>
+          <t>Hử? Tao chỉ làm theo những gì ghi trong kho lưu trữ thôi mà...</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Ui da... Đầu ta đau quá... Ngươi là ai?</t>
+          <t>Ui da... Đầu tao đau quá... Mày là ai?</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ta đấm hắn thêm phát nữa được không?</t>
+          <t>Tao đấm hắn thêm phát nữa được không?</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thuyền của ta đâu rồi? Ta đến đây kiểu gì thế này... Hả?</t>
+          <t>Thuyền của tao đâu rồi? Tao đến đây kiểu gì thế này... Hả?</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Ui... Đầu ta... đau quá...</t>
+          <t>Ui... Đầu tao... đau quá...</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Nếu Starbuck không lừa ta, thì cơn bão kia và tiếng hú đang cấu kết với nhau. Điều đó có nghĩa là...</t>
+          <t>Nếu Starbuck không lừa tao, thì cơn bão kia và tiếng hú đang cấu kết với nhau. Điều đó có nghĩa là...</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nào, {Male=cậu bé;Female=cô bé}. Cậu thử xem sao!</t>
+          <t>Nào, {Male=laddie;Female=missy}. Cậu thử xem sao!</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Đồ khốn, con quái vật máu lạnh mà ta đã vật lộn bao lâu để chế ngự...</t>
+          <t>Đồ khốn, con quái vật máu lạnh mà tao đã vật lộn bao lâu để chế ngự...</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Thật lòng mà nói, ta chẳng biết tí gì cả. À mà cậu đang ở đâu thế?</t>
+          <t>Thật lòng mà nói, tao chẳng biết tí gì cả. À mà cậu đang ở đâu thế?</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Chưa xong.</t>
+          <t>Chưa.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Run!</t>
+          <t>Chạy đi!</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Đ-Đ-Đợi đã, cậu định đi đâu thế? Ta sẽ bắt được con cá voi đó một ngày nào đó. Đợi mà xem!</t>
+          <t>Đ-Đ-Đợi đã, cậu định đi đâu thế? Tao sẽ bắt được con cá voi đó một ngày nào đó. Đợi mà xem!</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Cậu bị lừa gạt trong Carnevale... Ta biết một kẻ như ta chẳng đủ tư cách đại diện cho Order...</t>
+          <t>Cậu bị lừa gạt trong Carnevale... Tao biết một kẻ như tao chẳng đủ tư cách đại diện cho Order...</t>
         </is>
       </c>
     </row>
@@ -21049,7 +21049,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Ta tin rằng Đại úy Ahab cũng mong ngươi sẽ kế thừa di sản của ông ấy...</t>
+          <t>Tao tin rằng Đại úy Ahab cũng mong mày sẽ kế thừa di sản của ông ấy...</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Này, {Male=chú ngươi;Female=chị kia}, đừng có đứng đó nữa! Giúp ta một tay với cái này đi!</t>
+          <t>Này, {Male=laddie;Female=missy}, đừng có đứng đó nữa! Giúp tao một tay với cái này đi!</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Thằng to xác như thế à? Nó sẽ không thoát khỏi tay ta đâu, chỉ là vấn đề thời gian thôi, chẳng có gì phải lo.</t>
+          <t>Thằng to xác như thế à? Nó sẽ không thoát khỏi tay tao đâu, chỉ là vấn đề thời gian thôi, chẳng có gì phải lo.</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>À, chuyện đó à? Pff, có gì đâu. Hồi trẻ, ta có thể săn cá voi cả ngày cơ!</t>
+          <t>À, chuyện đó à? Pff, có gì đâu. Hồi trẻ, tao có thể săn cá voi cả ngày cơ!</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Này, nhìn kìa. Không phải đó là Cộng Hưởng Giả xuất hiện ở Ragunna hồi trước sao? Người đoạt giải ấy…</t>
+          <t>Này, nhìn kìa. Không phải đó là Resonator xuất hiện ở Ragunna hồi trước sao? Người đoạt giải ấy…</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25469,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Nếu còn phàn nàn gì nữa, cứ việc đổ hết lên đầu ta. Vui chưa? Giờ thì r?i ?i.</t>
+          <t>Nếu còn phàn nàn gì nữa, cứ việc đổ hết lên đầu ta. Vui chưa? Giờ thì cút đi.</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mũ của ta á? Ờ... ờ...</t>
+          <t>Mũ của tao á? Ờ... ờ...</t>
         </is>
       </c>
     </row>
@@ -26769,7 +26769,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Ta cũng chả biết cô ta đang bày trò gì nữa!</t>
+          <t>Tao cũng chả biết cô ta đang bày trò gì nữa!</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đem gỗ cho ta.</t>
+          <t>Đem gỗ cho tao.</t>
         </is>
       </c>
     </row>
